--- a/Atana-Governance-RACI-v1.0.xlsx
+++ b/Atana-Governance-RACI-v1.0.xlsx
@@ -4957,199 +4957,4 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
-    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{636D7984-44AA-490E-A65E-37067B27FD63}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AF306A9-1822-49A0-B067-FD56B776F190}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{198AF6E3-04D5-4272-A620-E6C1B3642B3F}"/>
 </file>
--- a/Atana-Governance-RACI-v1.0.xlsx
+++ b/Atana-Governance-RACI-v1.0.xlsx
@@ -4957,4 +4957,199 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
+    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E6091EE-7EEC-434B-A07A-E49950085805}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6227BF2F-DB79-48F1-B4A8-F7BED65BD2CF}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAE15FD6-3998-4A45-9628-39B4E340A338}"/>
 </file>
--- a/Atana-Governance-RACI-v1.0.xlsx
+++ b/Atana-Governance-RACI-v1.0.xlsx
@@ -4957,199 +4957,4 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
-    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E6091EE-7EEC-434B-A07A-E49950085805}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6227BF2F-DB79-48F1-B4A8-F7BED65BD2CF}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAE15FD6-3998-4A45-9628-39B4E340A338}"/>
 </file>
--- a/Atana-Governance-RACI-v1.0.xlsx
+++ b/Atana-Governance-RACI-v1.0.xlsx
@@ -4957,4 +4957,199 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
+    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D19D6DE1-EE42-4258-91DE-0C8CD0A34F9F}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFB1A88A-0DEB-433F-951B-C93F91582774}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C58BC4F-0DB6-4876-8AD9-D3AD5B771E25}"/>
 </file>
--- a/Atana-Governance-RACI-v1.0.xlsx
+++ b/Atana-Governance-RACI-v1.0.xlsx
@@ -4957,199 +4957,4 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
-    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D19D6DE1-EE42-4258-91DE-0C8CD0A34F9F}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFB1A88A-0DEB-433F-951B-C93F91582774}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C58BC4F-0DB6-4876-8AD9-D3AD5B771E25}"/>
 </file>
--- a/Atana-Governance-RACI-v1.0.xlsx
+++ b/Atana-Governance-RACI-v1.0.xlsx
@@ -4957,4 +4957,199 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
+    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0807DD50-DA4C-4FFA-A4BD-C4A974374216}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D4010E3-C556-4A02-807A-458C869ADF0D}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3355072A-017A-4956-9D8A-9524D5433354}"/>
 </file>
--- a/Atana-Governance-RACI-v1.0.xlsx
+++ b/Atana-Governance-RACI-v1.0.xlsx
@@ -4957,199 +4957,4 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
-    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0807DD50-DA4C-4FFA-A4BD-C4A974374216}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D4010E3-C556-4A02-807A-458C869ADF0D}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3355072A-017A-4956-9D8A-9524D5433354}"/>
 </file>
--- a/Atana-Governance-RACI-v1.0.xlsx
+++ b/Atana-Governance-RACI-v1.0.xlsx
@@ -4957,4 +4957,199 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
+    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FB2DDE0-2DBC-4377-8BAD-C03523D2119E}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{726100F6-4C04-470F-AE25-E4895DCB53AF}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{697B5204-8650-4D29-9752-4A8F39D5E14D}"/>
 </file>
--- a/Atana-Governance-RACI-v1.0.xlsx
+++ b/Atana-Governance-RACI-v1.0.xlsx
@@ -4957,199 +4957,4 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
-    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FB2DDE0-2DBC-4377-8BAD-C03523D2119E}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{726100F6-4C04-470F-AE25-E4895DCB53AF}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{697B5204-8650-4D29-9752-4A8F39D5E14D}"/>
 </file>
--- a/Atana-Governance-RACI-v1.0.xlsx
+++ b/Atana-Governance-RACI-v1.0.xlsx
@@ -4957,4 +4957,199 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
+    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{207EF448-A5AE-4151-B6F4-C43E38D23B6F}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29BD72A1-DA1E-4F38-A09E-C793CAD01C3A}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9ABA7FDB-8D30-480F-838B-68FFBA78EE84}"/>
 </file>
--- a/Atana-Governance-RACI-v1.0.xlsx
+++ b/Atana-Governance-RACI-v1.0.xlsx
@@ -4957,199 +4957,4 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
-    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{207EF448-A5AE-4151-B6F4-C43E38D23B6F}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29BD72A1-DA1E-4F38-A09E-C793CAD01C3A}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9ABA7FDB-8D30-480F-838B-68FFBA78EE84}"/>
 </file>
--- a/Atana-Governance-RACI-v1.0.xlsx
+++ b/Atana-Governance-RACI-v1.0.xlsx
@@ -4957,4 +4957,199 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
+    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70BED2C8-603F-4E36-997B-DD18C03ABA32}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04093F64-66EE-4A40-8712-D0F674EAA679}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA1C86E0-AF71-4505-A57B-EB978A3DCC8B}"/>
 </file>
--- a/Atana-Governance-RACI-v1.0.xlsx
+++ b/Atana-Governance-RACI-v1.0.xlsx
@@ -4957,199 +4957,4 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
-    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70BED2C8-603F-4E36-997B-DD18C03ABA32}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04093F64-66EE-4A40-8712-D0F674EAA679}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA1C86E0-AF71-4505-A57B-EB978A3DCC8B}"/>
 </file>
--- a/Atana-Governance-RACI-v1.0.xlsx
+++ b/Atana-Governance-RACI-v1.0.xlsx
@@ -4957,4 +4957,199 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
+    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93458971-71F4-45DD-ABCB-D65F92FB5AE7}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18CAA30A-A5DA-48F5-A26C-9918C02D0D4E}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB6913DC-5E99-490A-AA5D-C475A23FC32D}"/>
 </file>
--- a/Atana-Governance-RACI-v1.0.xlsx
+++ b/Atana-Governance-RACI-v1.0.xlsx
@@ -4957,199 +4957,4 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
-    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93458971-71F4-45DD-ABCB-D65F92FB5AE7}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18CAA30A-A5DA-48F5-A26C-9918C02D0D4E}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB6913DC-5E99-490A-AA5D-C475A23FC32D}"/>
 </file>
--- a/Atana-Governance-RACI-v1.0.xlsx
+++ b/Atana-Governance-RACI-v1.0.xlsx
@@ -4957,4 +4957,199 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
+    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{176594FA-CCFA-4402-805B-43276B050E2E}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8F39251-E0D0-475F-B2C2-A514D4493A65}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78E3D64B-3615-4050-9154-65D335D06BA1}"/>
 </file>
--- a/Atana-Governance-RACI-v1.0.xlsx
+++ b/Atana-Governance-RACI-v1.0.xlsx
@@ -4957,199 +4957,4 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
-    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{176594FA-CCFA-4402-805B-43276B050E2E}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8F39251-E0D0-475F-B2C2-A514D4493A65}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78E3D64B-3615-4050-9154-65D335D06BA1}"/>
 </file>
--- a/Atana-Governance-RACI-v1.0.xlsx
+++ b/Atana-Governance-RACI-v1.0.xlsx
@@ -4957,4 +4957,199 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
+    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8DAAA075-8DDC-4148-804D-77B24295914C}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE344905-381B-4E4A-9076-9A449FA64A3C}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EC3299A-DE05-48C7-8A02-BE91E904E10A}"/>
 </file>
--- a/Atana-Governance-RACI-v1.0.xlsx
+++ b/Atana-Governance-RACI-v1.0.xlsx
@@ -4957,199 +4957,4 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
-    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8DAAA075-8DDC-4148-804D-77B24295914C}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE344905-381B-4E4A-9076-9A449FA64A3C}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EC3299A-DE05-48C7-8A02-BE91E904E10A}"/>
 </file>